--- a/DATA/분위수별_회귀분석결과.xlsx
+++ b/DATA/분위수별_회귀분석결과.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Avg_Ret_N_구간</t>
+          <t>구간</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
